--- a/artfynd/A 29622-2025 artfynd.xlsx
+++ b/artfynd/A 29622-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -899,6 +899,124 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128073800</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57669</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Torpängen/Torpängsgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>558502</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6461670</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hackspår efter födosök</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Charlotte Erbs</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Charlotte Erbs</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29622-2025 artfynd.xlsx
+++ b/artfynd/A 29622-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128064353</v>
       </c>
       <c r="B2" t="n">
-        <v>58147</v>
+        <v>58153</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>128064366</v>
       </c>
       <c r="B3" t="n">
-        <v>57824</v>
+        <v>57830</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29622-2025 artfynd.xlsx
+++ b/artfynd/A 29622-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128064353</v>
       </c>
       <c r="B2" t="n">
-        <v>58153</v>
+        <v>58154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>128064366</v>
       </c>
       <c r="B3" t="n">
-        <v>57830</v>
+        <v>57831</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>128073800</v>
       </c>
       <c r="B4" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29622-2025 artfynd.xlsx
+++ b/artfynd/A 29622-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128064353</v>
       </c>
       <c r="B2" t="n">
-        <v>58154</v>
+        <v>58166</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>128064366</v>
       </c>
       <c r="B3" t="n">
-        <v>57831</v>
+        <v>57843</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>128073800</v>
       </c>
       <c r="B4" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29622-2025 artfynd.xlsx
+++ b/artfynd/A 29622-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128064353</v>
       </c>
       <c r="B2" t="n">
-        <v>58166</v>
+        <v>58170</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>128064366</v>
       </c>
       <c r="B3" t="n">
-        <v>57843</v>
+        <v>57847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>128073800</v>
       </c>
       <c r="B4" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29622-2025 artfynd.xlsx
+++ b/artfynd/A 29622-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128064353</v>
+        <v>128073800</v>
       </c>
       <c r="B2" t="n">
-        <v>58170</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103018</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -716,7 +716,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -726,13 +726,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558573</v>
+        <v>558502</v>
       </c>
       <c r="R2" t="n">
-        <v>6461650</v>
+        <v>6461670</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,6 +762,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hackspår efter födosök</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128064366</v>
+        <v>126826479</v>
       </c>
       <c r="B3" t="n">
-        <v>57847</v>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -799,39 +804,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -839,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558575</v>
+        <v>558557</v>
       </c>
       <c r="R3" t="n">
-        <v>6461643</v>
+        <v>6461685</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,12 +861,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,28 +875,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Charlotte Erbs</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Charlotte Erbs</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128073800</v>
+        <v>128063881</v>
       </c>
       <c r="B4" t="n">
-        <v>57686</v>
+        <v>57966</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,16 +905,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -942,7 +935,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -952,13 +945,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558502</v>
+        <v>558685</v>
       </c>
       <c r="R4" t="n">
-        <v>6461670</v>
+        <v>6461622</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,17 +975,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Hackspår efter födosök</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,14 +1007,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134282676</v>
+        <v>128074114</v>
       </c>
       <c r="B5" t="n">
-        <v>57972</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1048,24 +1036,28 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>bobygge</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Torpängen/Missmyra, Ög</t>
+          <t>Torpängen/Torpängsgölen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558653</v>
+        <v>558710</v>
       </c>
       <c r="R5" t="n">
-        <v>6461620</v>
+        <v>6461648</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1092,17 +1084,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Hackspår av födosök</t>
+          <t>Tre bohål i samma asp</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,22 +1109,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sigrid Gustafsson</t>
+          <t>Charlotte Erbs</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sigrid Gustafsson</t>
+          <t>Charlotte Erbs</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134281736</v>
+        <v>134281797</v>
       </c>
       <c r="B6" t="n">
-        <v>8449</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,28 +1132,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1207,13 +1202,17 @@
           <t>2026-06-07</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hackspår av födosök</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1232,14 +1231,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134281797</v>
+        <v>134282676</v>
       </c>
       <c r="B7" t="n">
         <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1275,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558666</v>
+        <v>558653</v>
       </c>
       <c r="R7" t="n">
-        <v>6461611</v>
+        <v>6461620</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1349,7 +1348,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1449,6 +1448,1128 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>117377929</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58435</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100058</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mindre flugsnappare</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ficedula parva</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1794)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Torpängen, Missmyra våtmark, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>558713</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6461716</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Elis Ölfvingsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Stefan Adolfsson, Random Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>116911289</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57942</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102119</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Göktyta</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Jynx torquilla</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Torpängen, Missmyra våtmark, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>558713</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6461716</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Stefan Adolfsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Stefan Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134280527</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57964</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>102119</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Göktyta</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Jynx torquilla</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Torpängen/Missmyra, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>558730</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6461589</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sigrid Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sigrid Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>116911273</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58238</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Torpängen, Missmyra våtmark, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>558713</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6461716</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Stefan Adolfsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Stefan Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134282761</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58349</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Torpängen/Missmyra, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>558689</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6461613</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sigrid Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Sigrid Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128064353</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Torpängen/Torpängsgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>558573</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6461650</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Charlotte Erbs</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Charlotte Erbs</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128064366</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Torpängen/Torpängsgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>558575</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6461643</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Charlotte Erbs</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Charlotte Erbs</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128064694</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Torpängen/Torpängsgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>558677</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6461610</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Charlotte Erbs</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Charlotte Erbs</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134281736</v>
+      </c>
+      <c r="B17" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Torpängen/Missmyra, Ög</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>558666</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6461611</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Sigrid Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Sigrid Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134282788</v>
+      </c>
+      <c r="B18" t="n">
+        <v>102637</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Torpängen/Missmyra, Ög</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>558511</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6461549</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Många</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Sigrid Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Sigrid Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
